--- a/sheets/대금율보/검수/흥타령.xlsx
+++ b/sheets/대금율보/검수/흥타령.xlsx
@@ -10414,43 +10414,28 @@
         </is>
       </c>
       <c r="C8" s="25"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="23"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="G8" s="23"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="23"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="K8" s="23"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="23"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="O8" s="23" t="inlineStr">
@@ -10460,8 +10445,7 @@
       </c>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="Q8" s="23" t="inlineStr">
@@ -10471,8 +10455,7 @@
       </c>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="S8" s="23"/>
@@ -10667,8 +10650,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="C11" s="22"/>
@@ -10967,38 +10949,33 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M14" s="26"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="O14" s="26" t="inlineStr">
@@ -11009,15 +10986,13 @@
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="Q14" s="26"/>
       <c r="R14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="S14" s="26" t="inlineStr">
@@ -11484,28 +11459,21 @@
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="C22" s="23"/>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="E22" s="23"/>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F22" s="21"/>
       <c r="G22" s="23"/>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -11517,8 +11485,7 @@
       <c r="K22" s="23"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
@@ -11538,8 +11505,7 @@
       <c r="S22" s="23"/>
       <c r="T22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="U22" s="23" t="inlineStr">
@@ -11741,11 +11707,7 @@
       <c r="K25" s="22"/>
       <c r="L25" s="21"/>
       <c r="M25" s="22"/>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N25" s="21"/>
       <c r="O25" s="22"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="22"/>
@@ -11941,8 +11903,7 @@
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
@@ -11952,8 +11913,7 @@
       </c>
       <c r="D28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr">
@@ -11963,8 +11923,7 @@
       </c>
       <c r="F28" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋⌇
-‹</t>
+          <t xml:space="preserve">淋⌇</t>
         </is>
       </c>
       <c r="G28" s="26" t="inlineStr">
@@ -12298,8 +12257,7 @@
       <c r="Q36" s="23"/>
       <c r="R36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="S36" s="23" t="inlineStr">
@@ -12309,8 +12267,7 @@
       </c>
       <c r="T36" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="U36" s="23"/>
@@ -12574,8 +12531,7 @@
       <c r="P42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="Q42" s="26" t="inlineStr">
@@ -12585,15 +12541,13 @@
       </c>
       <c r="R42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧
-‹</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="S42" s="26"/>
       <c r="T42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="U42" s="26" t="inlineStr">

--- a/sheets/대금율보/검수/흥타령.xlsx
+++ b/sheets/대금율보/검수/흥타령.xlsx
@@ -9886,32 +9886,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="119.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="119.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="119.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -10250,7 +10250,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="119.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="26"/>
@@ -10333,7 +10333,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="119.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="U7" s="27"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="119.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="24" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="119.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="26"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="119.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="119.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="119.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="119.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -11008,10 +11008,10 @@
       </c>
       <c r="U14" s="26"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="80.0" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="119.22" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="119.22" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="119.22" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="U19" s="25"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="119.22" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="119.22" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="119.22" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="119.22" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="119.22" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="119.22" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="U25" s="27"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="119.22" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="119.22" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="119.22" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -11977,10 +11977,10 @@
       </c>
       <c r="U28" s="26"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="80.0" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="119.22" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21"/>
       <c r="C31" s="22"/>
@@ -12064,7 +12064,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="119.22" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21"/>
       <c r="C32" s="23"/>
@@ -12103,7 +12103,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="119.22" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="23"/>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="119.22" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21"/>
       <c r="C34" s="26"/>
@@ -12202,7 +12202,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="119.22" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21"/>
       <c r="C35" s="22"/>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="U35" s="27"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="119.22" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21"/>
       <c r="C36" s="23"/>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="U36" s="23"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="119.22" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21"/>
       <c r="C37" s="23"/>
@@ -12320,7 +12320,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="119.22" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21"/>
       <c r="C38" s="26"/>
@@ -12356,7 +12356,7 @@
       <c r="T38" s="21"/>
       <c r="U38" s="26"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="119.22" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21"/>
       <c r="C39" s="22"/>
@@ -12400,7 +12400,7 @@
       <c r="T39" s="21"/>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="119.22" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21"/>
       <c r="C40" s="23"/>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="119.22" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21"/>
       <c r="C41" s="23"/>
@@ -12507,7 +12507,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="119.22" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21"/>
       <c r="C42" s="26"/>
@@ -12564,7 +12564,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
